--- a/AAII_Financials/Yearly/LCID_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LCID_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,46 +656,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
@@ -708,27 +709,30 @@
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>595300</v>
+      </c>
+      <c r="E8" s="3">
         <v>608200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>27100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4600</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -738,30 +742,33 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1936100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1646100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>154900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3900</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -774,27 +781,30 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1340800</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1037900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-127800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>700</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -807,9 +817,12 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,26 +836,27 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>937000</v>
+      </c>
+      <c r="E12" s="3">
         <v>821500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>750200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>511100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>220200</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +869,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,21 +905,24 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>24500</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>2700</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -918,12 +938,15 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -954,9 +977,12 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,26 +993,27 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3694900</v>
+      </c>
+      <c r="E17" s="3">
         <v>3202200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1560300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>603200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>262500</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
       </c>
@@ -999,27 +1026,30 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3099600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2594000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1533200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-599200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-257900</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1032,9 +1062,12 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,26 +1081,27 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>297100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1292400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1046100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-120300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10900</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,27 +1114,30 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2568900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1115000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2516300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-709300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-264900</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1110,30 +1147,33 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E22" s="3">
         <v>2500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8500</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1143,30 +1183,33 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2827400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1304100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2579700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-719600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-277300</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1179,26 +1222,29 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1212,9 +1258,12 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,27 +1294,30 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2828400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1304500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2579800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-719400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-277400</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1278,27 +1330,30 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2828400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2558700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4747100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-705600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-269400</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1311,9 +1366,12 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1402,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1438,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1474,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,27 +1510,30 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-297100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1292400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1046100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>120300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10900</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1476,27 +1546,30 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2828400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2558700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4747100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-705600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-269400</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1509,9 +1582,12 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,27 +1618,30 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2828400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2558700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4747100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-705600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-269400</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1575,32 +1654,35 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1613,9 +1695,12 @@
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1714,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,26 +1730,27 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1369900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1735800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6262900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>614400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>351700</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1676,26 +1763,29 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2489800</v>
+      </c>
+      <c r="E42" s="3">
         <v>2177200</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>500</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
+      <c r="H42" s="3">
+        <v>500</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
@@ -1706,30 +1796,33 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E43" s="3">
         <v>19500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1739,30 +1832,33 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>696200</v>
+      </c>
+      <c r="E44" s="3">
         <v>834400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>127300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>700</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1772,30 +1868,33 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>149400</v>
+      </c>
+      <c r="E45" s="3">
         <v>145100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>113700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>46300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>70000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,27 +1907,30 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4757200</v>
+      </c>
+      <c r="E46" s="3">
         <v>4912000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6507000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>662600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>423200</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1841,18 +1943,21 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>542500</v>
+      </c>
+      <c r="E47" s="3">
         <v>530000</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1868,33 +1973,36 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3032400</v>
+      </c>
+      <c r="E48" s="3">
         <v>2381900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1344100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>713300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>142800</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1904,12 +2012,15 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1940,9 +2051,12 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2087,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,27 +2123,30 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>180700</v>
+      </c>
+      <c r="E52" s="3">
         <v>55300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>30600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13600</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2036,12 +2156,15 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,27 +2195,30 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8512700</v>
+      </c>
+      <c r="E54" s="3">
         <v>7879200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7881700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1402700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>579600</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2105,9 +2231,12 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2250,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,26 +2266,27 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>108700</v>
+      </c>
+      <c r="E57" s="3">
         <v>229100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>41300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12700</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2168,24 +2299,27 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E58" s="3">
         <v>20200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1000</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2198,30 +2332,33 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>819000</v>
+      </c>
+      <c r="E59" s="3">
         <v>688300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>335300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>167000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>84000</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,27 +2371,30 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1008400</v>
+      </c>
+      <c r="E60" s="3">
         <v>937600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>396100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>185300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>96700</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2267,27 +2407,30 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2074600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2073200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1992900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>200</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2300,27 +2443,30 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>578000</v>
+      </c>
+      <c r="E62" s="3">
         <v>518800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1583400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>40100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>29700</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,9 +2479,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2515,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2551,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,27 +2587,30 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3661000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3529500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3972400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>227400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>126700</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2465,9 +2623,12 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2642,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2675,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2711,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2559,14 +2727,14 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
         <v>2494100</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>1074000</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -2579,9 +2747,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,27 +2783,30 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10198800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1356900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-637500</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,9 +2819,12 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2855,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2891,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,27 +2927,30 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4851700</v>
+      </c>
+      <c r="E76" s="3">
         <v>4349700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3909400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1318800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-621100</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2963,12 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,32 +2999,35 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2848,27 +3040,30 @@
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2828400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2558700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4747100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-705600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-269400</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2881,9 +3076,12 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,26 +3095,27 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>233500</v>
+      </c>
+      <c r="E83" s="3">
         <v>186600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>62900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3800</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,12 +3125,15 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3164,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3200,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3236,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3272,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,27 +3308,30 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2489800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2226300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1058100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-570200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-235300</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3127,9 +3344,12 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,26 +3363,27 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-910600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1074900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-421200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-459600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-104300</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3172,12 +3393,15 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3432,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,27 +3468,30 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-947000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3681700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-420700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-459600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-104300</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,9 +3504,12 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,8 +3523,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3322,9 +3556,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3592,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3628,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,27 +3664,30 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3070900</v>
+      </c>
+      <c r="E100" s="3">
         <v>1347200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>7136400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1290500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>621400</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3454,9 +3700,12 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3487,27 +3736,30 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-365800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4560700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5657600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>260800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>281800</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3520,7 +3772,10 @@
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LCID_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LCID_YR_FIN.xlsx
@@ -1091,10 +1091,10 @@
         <v>297100</v>
       </c>
       <c r="E20" s="3">
-        <v>1292400</v>
+        <v>1320500</v>
       </c>
       <c r="F20" s="3">
-        <v>-1046100</v>
+        <v>-1045200</v>
       </c>
       <c r="G20" s="3">
         <v>-120300</v>
@@ -1127,10 +1127,10 @@
         <v>-2568900</v>
       </c>
       <c r="E21" s="3">
-        <v>-1115000</v>
+        <v>-1086900</v>
       </c>
       <c r="F21" s="3">
-        <v>-2516300</v>
+        <v>-2515400</v>
       </c>
       <c r="G21" s="3">
         <v>-709300</v>
@@ -1163,10 +1163,10 @@
         <v>24900</v>
       </c>
       <c r="E22" s="3">
-        <v>2500</v>
+        <v>30600</v>
       </c>
       <c r="F22" s="3">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="G22" s="3">
         <v>100</v>
@@ -1523,10 +1523,10 @@
         <v>-297100</v>
       </c>
       <c r="E32" s="3">
-        <v>-1292400</v>
+        <v>-1320500</v>
       </c>
       <c r="F32" s="3">
-        <v>1046100</v>
+        <v>1045200</v>
       </c>
       <c r="G32" s="3">
         <v>120300</v>

--- a/AAII_Financials/Yearly/LCID_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LCID_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>LCID</t>
   </si>
@@ -915,10 +915,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>24500</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+        <v>18500</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>2700</v>
@@ -951,19 +951,19 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>233500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>186600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>62900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1000,13 +1000,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3694900</v>
+        <v>3670300</v>
       </c>
       <c r="E17" s="3">
         <v>3202200</v>
       </c>
       <c r="F17" s="3">
-        <v>1560300</v>
+        <v>1557600</v>
       </c>
       <c r="G17" s="3">
         <v>603200</v>
@@ -1036,13 +1036,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3099600</v>
+        <v>-3075000</v>
       </c>
       <c r="E18" s="3">
         <v>-2594000</v>
       </c>
       <c r="F18" s="3">
-        <v>-1533200</v>
+        <v>-1530400</v>
       </c>
       <c r="G18" s="3">
         <v>-599200</v>
@@ -1088,19 +1088,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>297100</v>
+        <v>-86800</v>
       </c>
       <c r="E20" s="3">
-        <v>1320500</v>
+        <v>-1263800</v>
       </c>
       <c r="F20" s="3">
-        <v>-1045200</v>
+        <v>1045200</v>
       </c>
       <c r="G20" s="3">
-        <v>-120300</v>
+        <v>120300</v>
       </c>
       <c r="H20" s="3">
-        <v>-10900</v>
+        <v>10900</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1124,13 +1124,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-2568900</v>
+        <v>-2754700</v>
       </c>
       <c r="E21" s="3">
-        <v>-1086900</v>
+        <v>-1143700</v>
       </c>
       <c r="F21" s="3">
-        <v>-2515400</v>
+        <v>-2512700</v>
       </c>
       <c r="G21" s="3">
         <v>-709300</v>
@@ -1138,11 +1138,11 @@
       <c r="H21" s="3">
         <v>-264900</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1343,7 +1343,7 @@
         <v>-2828400</v>
       </c>
       <c r="E27" s="3">
-        <v>-2558700</v>
+        <v>-1304500</v>
       </c>
       <c r="F27" s="3">
         <v>-4747100</v>
@@ -1520,19 +1520,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-297100</v>
+        <v>86800</v>
       </c>
       <c r="E32" s="3">
-        <v>-1320500</v>
+        <v>1263800</v>
       </c>
       <c r="F32" s="3">
-        <v>1045200</v>
+        <v>-1045200</v>
       </c>
       <c r="G32" s="3">
-        <v>120300</v>
+        <v>-120300</v>
       </c>
       <c r="H32" s="3">
-        <v>10900</v>
+        <v>-10900</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1559,16 +1559,16 @@
         <v>-2828400</v>
       </c>
       <c r="E33" s="3">
-        <v>-2558700</v>
+        <v>-1304500</v>
       </c>
       <c r="F33" s="3">
-        <v>-4747100</v>
+        <v>-2579800</v>
       </c>
       <c r="G33" s="3">
-        <v>-705600</v>
+        <v>-719400</v>
       </c>
       <c r="H33" s="3">
-        <v>-269400</v>
+        <v>-277400</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
@@ -1631,16 +1631,16 @@
         <v>-2828400</v>
       </c>
       <c r="E35" s="3">
-        <v>-2558700</v>
+        <v>-1304500</v>
       </c>
       <c r="F35" s="3">
-        <v>-4747100</v>
+        <v>-2579800</v>
       </c>
       <c r="G35" s="3">
-        <v>-705600</v>
+        <v>-719400</v>
       </c>
       <c r="H35" s="3">
-        <v>-269400</v>
+        <v>-277400</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
@@ -1787,11 +1787,11 @@
       <c r="H42" s="3">
         <v>500</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1809,10 +1809,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>51800</v>
+        <v>62900</v>
       </c>
       <c r="E43" s="3">
-        <v>19500</v>
+        <v>27000</v>
       </c>
       <c r="F43" s="3">
         <v>3100</v>
@@ -1821,7 +1821,7 @@
         <v>300</v>
       </c>
       <c r="H43" s="3">
-        <v>400</v>
+        <v>20900</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1881,19 +1881,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>149400</v>
+        <v>67000</v>
       </c>
       <c r="E45" s="3">
-        <v>145100</v>
+        <v>72500</v>
       </c>
       <c r="F45" s="3">
-        <v>113700</v>
+        <v>32600</v>
       </c>
       <c r="G45" s="3">
-        <v>46300</v>
+        <v>13200</v>
       </c>
       <c r="H45" s="3">
-        <v>70000</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -2039,11 +2039,11 @@
       <c r="H49" s="3">
         <v>0</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2309,19 +2309,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>80700</v>
+        <v>109200</v>
       </c>
       <c r="E58" s="3">
-        <v>20200</v>
+        <v>31500</v>
       </c>
       <c r="F58" s="3">
-        <v>19500</v>
+        <v>15200</v>
       </c>
       <c r="G58" s="3">
         <v>1000</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="H58" s="3">
+        <v>0</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2345,19 +2345,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>819000</v>
+        <v>569400</v>
       </c>
       <c r="E59" s="3">
-        <v>688300</v>
+        <v>392900</v>
       </c>
       <c r="F59" s="3">
-        <v>335300</v>
+        <v>247000</v>
       </c>
       <c r="G59" s="3">
-        <v>167000</v>
+        <v>96200</v>
       </c>
       <c r="H59" s="3">
-        <v>84000</v>
+        <v>37900</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2390,10 +2390,10 @@
         <v>396100</v>
       </c>
       <c r="G60" s="3">
-        <v>185300</v>
+        <v>182300</v>
       </c>
       <c r="H60" s="3">
-        <v>96700</v>
+        <v>65900</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2417,16 +2417,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2074600</v>
+        <v>2318700</v>
       </c>
       <c r="E61" s="3">
-        <v>2073200</v>
+        <v>2317000</v>
       </c>
       <c r="F61" s="3">
-        <v>1992900</v>
+        <v>2178200</v>
       </c>
       <c r="G61" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>200</v>
@@ -2453,19 +2453,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>578000</v>
+        <v>226100</v>
       </c>
       <c r="E62" s="3">
-        <v>518800</v>
+        <v>275000</v>
       </c>
       <c r="F62" s="3">
-        <v>1583400</v>
+        <v>1398100</v>
       </c>
       <c r="G62" s="3">
-        <v>40100</v>
+        <v>39100</v>
       </c>
       <c r="H62" s="3">
-        <v>29700</v>
+        <v>58800</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2606,10 +2606,10 @@
         <v>3972400</v>
       </c>
       <c r="G66" s="3">
-        <v>227400</v>
+        <v>221400</v>
       </c>
       <c r="H66" s="3">
-        <v>126700</v>
+        <v>124900</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2730,10 +2730,10 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>2494100</v>
+        <v>2500000</v>
       </c>
       <c r="H70" s="3">
-        <v>1074000</v>
+        <v>1075800</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -3053,16 +3053,16 @@
         <v>-2828400</v>
       </c>
       <c r="E81" s="3">
-        <v>-2558700</v>
+        <v>-1304500</v>
       </c>
       <c r="F81" s="3">
-        <v>-4747100</v>
+        <v>-2579800</v>
       </c>
       <c r="G81" s="3">
-        <v>-705600</v>
+        <v>-719400</v>
       </c>
       <c r="H81" s="3">
-        <v>-269400</v>
+        <v>-277400</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
@@ -3709,26 +3709,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3760,11 +3760,11 @@
       <c r="H102" s="3">
         <v>281800</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/LCID_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LCID_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>LCID</t>
   </si>
@@ -656,50 +656,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -712,30 +712,33 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>807800</v>
+      </c>
+      <c r="E8" s="3">
         <v>595300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>608200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>27100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4600</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -745,33 +748,36 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1730900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1936100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1646100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>154900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3900</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -784,30 +790,33 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-923100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1340800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1037900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-127800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>700</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -820,9 +829,12 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,29 +849,30 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1176500</v>
+      </c>
+      <c r="E12" s="3">
         <v>937000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>821500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>750200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>511100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>220200</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
@@ -872,9 +885,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -908,24 +924,27 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E14" s="3">
         <v>18500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>2700</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -941,33 +960,36 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>295300</v>
+      </c>
+      <c r="E15" s="3">
         <v>233500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>186600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>62900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3800</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
@@ -980,9 +1002,12 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -994,29 +1019,30 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3808300</v>
+      </c>
+      <c r="E17" s="3">
         <v>3670300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3202200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1557600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>603200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>262500</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,30 +1055,33 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3000500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3075000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2594000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1530400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-599200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-257900</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1065,9 +1094,12 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1082,29 +1114,30 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-171000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-86800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1263800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1045200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>120300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>10900</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1117,66 +1150,72 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2534100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2754700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1143700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2512700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-709300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-264900</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E22" s="3">
         <v>24900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>30600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8500</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1186,33 +1225,36 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2712700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2827400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1304100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2579700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-719600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-277300</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,29 +1267,32 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1261,9 +1306,12 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1297,30 +1345,33 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2713900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2828400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1304500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2579800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-719400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-277400</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1333,30 +1384,33 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3061600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2828400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1304500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4747100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-705600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-269400</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1369,9 +1423,12 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1405,9 +1462,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1441,9 +1501,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1477,9 +1540,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1513,30 +1579,33 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E32" s="3">
         <v>86800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1263800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1045200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-120300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-10900</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1549,30 +1618,33 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2713900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2828400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1304500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2579800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-719400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-277400</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1585,9 +1657,12 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1621,30 +1696,33 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2713900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2828400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1304500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2579800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-719400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-277400</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1657,35 +1735,38 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1698,9 +1779,12 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1715,8 +1799,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1731,29 +1816,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1606900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1369900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1735800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6262900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>614400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>351700</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1766,66 +1852,72 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2424100</v>
+      </c>
+      <c r="E42" s="3">
         <v>2489800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2177200</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>500</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>131600</v>
+      </c>
+      <c r="E43" s="3">
         <v>62900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20900</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1835,33 +1927,36 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>407800</v>
+      </c>
+      <c r="E44" s="3">
         <v>696200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>834400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>127300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>700</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1871,33 +1966,36 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>250600</v>
+      </c>
+      <c r="E45" s="3">
         <v>67000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>72500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>32600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1910,30 +2008,33 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4873900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4757200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4912000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6507000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>662600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>423200</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1946,21 +2047,24 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>542500</v>
+        <v>1050100</v>
       </c>
       <c r="E47" s="3">
+        <v>542600</v>
+      </c>
+      <c r="F47" s="3">
         <v>530000</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1976,36 +2080,39 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3474500</v>
+      </c>
+      <c r="E48" s="3">
         <v>3032400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2381900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1344100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>713300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>142800</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2015,12 +2122,15 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2039,14 +2149,14 @@
       <c r="H49" s="3">
         <v>0</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2054,9 +2164,12 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2090,9 +2203,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2126,30 +2242,33 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>180700</v>
+        <v>249400</v>
       </c>
       <c r="E52" s="3">
+        <v>180600</v>
+      </c>
+      <c r="F52" s="3">
         <v>55300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>30600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13600</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2159,12 +2278,15 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2198,30 +2320,33 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9647900</v>
+      </c>
+      <c r="E54" s="3">
         <v>8512700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7879200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7881700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1402700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>579600</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,9 +2359,12 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2251,8 +2379,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2267,29 +2396,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>133800</v>
+      </c>
+      <c r="E57" s="3">
         <v>108700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>229100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12700</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,29 +2432,32 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>168800</v>
+      </c>
+      <c r="E58" s="3">
         <v>109200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>31500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2335,33 +2468,36 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>549400</v>
+      </c>
+      <c r="E59" s="3">
         <v>569400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>392900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>247000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>96200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>37900</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2374,30 +2510,33 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1165300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1008400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>937600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>396100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>182300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>65900</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2410,30 +2549,33 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2308100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2318700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2317000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2178200</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>200</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2446,30 +2588,33 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>889200</v>
+      </c>
+      <c r="E62" s="3">
         <v>226100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>275000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1398100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>39100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>58800</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2482,9 +2627,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2518,9 +2666,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2554,9 +2705,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2590,30 +2744,33 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4475300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3661000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3529500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3972400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>221400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>124900</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2626,9 +2783,12 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2643,8 +2803,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2678,9 +2839,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2714,14 +2878,17 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>1299800</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -2730,14 +2897,14 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>2500000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>1075800</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -2750,9 +2917,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2786,30 +2956,33 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12912700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10198800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1356900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-637500</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2822,9 +2995,12 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2858,9 +3034,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2894,9 +3073,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2930,30 +3112,33 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3872800</v>
+      </c>
+      <c r="E76" s="3">
         <v>4851700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4349700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3909400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1318800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-621100</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2966,9 +3151,12 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3002,35 +3190,38 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3043,30 +3234,33 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2713900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2828400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1304500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2579800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-719400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-277400</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3079,9 +3273,12 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3096,29 +3293,30 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>295300</v>
+      </c>
+      <c r="E83" s="3">
         <v>233500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>186600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>62900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3800</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3128,12 +3326,15 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3167,9 +3368,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3203,9 +3407,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3239,9 +3446,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3275,9 +3485,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3311,30 +3524,33 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2019700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2489800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2226300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1058100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-570200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-235300</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3347,9 +3563,12 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3364,29 +3583,30 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-883800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-910600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1074900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-421200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-459600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-104300</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3396,12 +3616,15 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3435,9 +3658,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3471,30 +3697,33 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1294500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-947000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3681700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-420700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-459600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-104300</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3507,9 +3736,12 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3524,8 +3756,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3559,9 +3792,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3595,9 +3831,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3631,9 +3870,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3667,30 +3909,33 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3549700</v>
+      </c>
+      <c r="E100" s="3">
         <v>3070900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1347200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>7136400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1290500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>621400</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3703,9 +3948,12 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3730,8 +3978,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3739,35 +3987,38 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>235500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-365800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4560700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5657600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>260800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>281800</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
@@ -3775,7 +4026,10 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LCID_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LCID_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>LCID</t>
   </si>
@@ -656,53 +656,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -715,33 +715,36 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1353800</v>
+      </c>
+      <c r="E8" s="3">
         <v>807800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>595300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>608200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>27100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4600</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -751,36 +754,39 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2610200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1730900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1936100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1646100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>154900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3900</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
@@ -793,33 +799,36 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1256400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-923100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1340800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1037900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-127800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>700</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -832,9 +841,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,32 +862,33 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1211400</v>
+      </c>
+      <c r="E12" s="3">
         <v>1176500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>937000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>821500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>750200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>511100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>220200</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
@@ -888,9 +901,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,27 +943,30 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-106000</v>
+      </c>
+      <c r="E14" s="3">
         <v>63400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>18500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>2700</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -963,36 +982,39 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>451200</v>
+      </c>
+      <c r="E15" s="3">
         <v>295300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>233500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>186600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>62900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>10200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3800</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -1005,9 +1027,12 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1020,32 +1045,33 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4855500</v>
+      </c>
+      <c r="E17" s="3">
         <v>3808300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3670300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3202200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1557600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>603200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>262500</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1058,33 +1084,36 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3501800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3000500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3075000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2594000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1530400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-599200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-257900</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1097,9 +1126,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1115,32 +1147,33 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-634000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-171000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-86800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1263800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1045200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>120300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>10900</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1153,72 +1186,78 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2416500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2534100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2754700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1143700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2512700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-709300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-264900</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
+      <c r="L21" s="3">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E22" s="3">
         <v>32900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>24900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8500</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1228,36 +1267,39 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2712700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2827400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1304100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2579700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-719600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-277300</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,32 +1312,35 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1309,9 +1354,12 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1348,33 +1396,36 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2698100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2713900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2828400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1304500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2579800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-719400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-277400</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1387,33 +1438,36 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3681700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3061600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2828400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1304500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4747100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-705600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-269400</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1426,9 +1480,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1465,9 +1522,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1504,9 +1564,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1543,9 +1606,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1582,33 +1648,36 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>634000</v>
+      </c>
+      <c r="E32" s="3">
         <v>171000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>86800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1263800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1045200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-120300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-10900</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,33 +1690,36 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2698100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2713900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2828400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1304500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2579800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-719400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-277400</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1660,9 +1732,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1699,33 +1774,36 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2698100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2713900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2828400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1304500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2579800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-719400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-277400</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,38 +1816,41 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1782,9 +1863,12 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1800,8 +1884,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1817,32 +1902,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>997800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1606900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1369900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1735800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6262900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>614400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>351700</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1855,72 +1941,78 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>631100</v>
+      </c>
+      <c r="E42" s="3">
         <v>2424100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2489800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2177200</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>500</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>190300</v>
+      </c>
+      <c r="E43" s="3">
         <v>131600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>62900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>20900</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1930,36 +2022,39 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1109500</v>
+      </c>
+      <c r="E44" s="3">
         <v>407800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>696200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>834400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>127300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>700</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1969,36 +2064,39 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>291500</v>
+      </c>
+      <c r="E45" s="3">
         <v>250600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>67000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>72500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>32600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2011,33 +2109,36 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3299700</v>
+      </c>
+      <c r="E46" s="3">
         <v>4873900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4757200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4912000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6507000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>662600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>423200</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2050,24 +2151,27 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>512200</v>
+      </c>
+      <c r="E47" s="3">
         <v>1050100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>542600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>530000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2083,39 +2187,42 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4220100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3474500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3032400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2381900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1344100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>713300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>142800</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2125,12 +2232,15 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2152,14 +2262,14 @@
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2167,9 +2277,12 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2206,9 +2319,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2245,33 +2361,36 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>355000</v>
+      </c>
+      <c r="E52" s="3">
         <v>249400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>180600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>55300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>30600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13600</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2281,12 +2400,15 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2323,33 +2445,36 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8387000</v>
+      </c>
+      <c r="E54" s="3">
         <v>9647900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8512700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7879200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7881700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1402700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>579600</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,9 +2487,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2380,8 +2508,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2397,32 +2526,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>487500</v>
+      </c>
+      <c r="E57" s="3">
         <v>133800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>108700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>229100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12700</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2435,32 +2565,35 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>820100</v>
+      </c>
+      <c r="E58" s="3">
         <v>168800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>109200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>31500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2471,36 +2604,39 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>549400</v>
+        <v>796400</v>
       </c>
       <c r="E59" s="3">
+        <v>527100</v>
+      </c>
+      <c r="F59" s="3">
         <v>569400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>392900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>247000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>96200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>37900</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2513,33 +2649,36 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2636100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1165300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1008400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>937600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>396100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>182300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>65900</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2552,33 +2691,36 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2376600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2308100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2318700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2317000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2178200</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>200</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2591,33 +2733,36 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>258700</v>
+      </c>
+      <c r="E62" s="3">
         <v>889200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>226100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>275000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1398100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>39100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>58800</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2630,9 +2775,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2669,9 +2817,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2708,9 +2859,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2747,33 +2901,36 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5386200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4475300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3661000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3529500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3972400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>221400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>124900</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2786,9 +2943,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2804,8 +2964,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2842,9 +3003,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2881,18 +3045,21 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2283500</v>
+      </c>
+      <c r="E70" s="3">
         <v>1299800</v>
       </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
       <c r="F70" s="3">
         <v>0</v>
       </c>
@@ -2900,14 +3067,14 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>2500000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>1075800</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -2920,9 +3087,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2959,33 +3129,36 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-15610700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-12912700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10198800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1356900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-637500</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,9 +3171,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3037,9 +3213,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3076,9 +3255,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3115,33 +3297,36 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>717300</v>
+      </c>
+      <c r="E76" s="3">
         <v>3872800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4851700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4349700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3909400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1318800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-621100</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3154,9 +3339,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3193,38 +3381,41 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3237,33 +3428,36 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2698100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2713900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2828400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1304500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2579800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-719400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-277400</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3276,9 +3470,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3294,32 +3491,33 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>451200</v>
+      </c>
+      <c r="E83" s="3">
         <v>295300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>233500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>186600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>62900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3800</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3329,12 +3527,15 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3371,9 +3572,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3410,9 +3614,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3449,9 +3656,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3488,9 +3698,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3527,33 +3740,36 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2931900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2019700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2489800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2226300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1058100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-570200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-235300</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3566,9 +3782,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3584,32 +3803,33 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-868200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-883800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-910600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1074900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-421200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-459600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-104300</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3619,12 +3839,15 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3661,9 +3884,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3700,33 +3926,36 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1478400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1294500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-947000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3681700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-420700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-459600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-104300</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,9 +3968,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3757,8 +3989,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3795,9 +4028,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3834,9 +4070,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3873,9 +4112,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3912,33 +4154,36 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>887300</v>
+      </c>
+      <c r="E100" s="3">
         <v>3549700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3070900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1347200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7136400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1290500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>621400</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3951,9 +4196,12 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3981,8 +4229,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -3990,38 +4238,41 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-566100</v>
+      </c>
+      <c r="E102" s="3">
         <v>235500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-365800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4560700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5657600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>260800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>281800</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
@@ -4029,7 +4280,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
